--- a/survey_templates/046_post_event_business_impact_survey--survey_templates.xlsx
+++ b/survey_templates/046_post_event_business_impact_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Event Name</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What was the name of the event?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please provide the name of the event.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -551,10 +555,14 @@
           <t>Event Date</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide the date of the event.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +579,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Event Organizer</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Who organized the event?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please specify the name of the event organizer.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +606,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rating</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How would you rate the event?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please rate the event from 1-5.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,13 +633,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Improvement Areas</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>What areas could we improve?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please specify the areas for improvement.</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -640,13 +660,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Recommendations</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Do you have any recommendations?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide any recommendations for future events.</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -666,10 +690,14 @@
           <t>Comments</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments.</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -689,10 +717,14 @@
           <t>Email</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide your email address.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,13 +741,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please provide your phone number.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -732,13 +768,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Event Attendance</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>How many attendees were present?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please select an option.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,13 +795,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Event Satisfaction</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>How satisfied were you with the event?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please select multiple options.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,13 +822,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Event Effectiveness</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>How effective was the event?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please select one option.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -801,13 +849,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Event Value</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>What value did you receive from the event?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please select multiple options.</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -824,13 +876,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Improvement Areas</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>What areas could we improve in future events?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Please select one option.</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -847,13 +903,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Recommendations</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Do you have any recommendations for future events?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please provide any recommendations.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -870,13 +930,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Comments 2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -893,197 +957,71 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Event Attendance</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>How many attendees were present at the event?</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please select an option.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>event_satisfaction_2</t>
+          <t>event_effectiveness_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Event Satisfaction</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>Event Effectiveness 2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please select one option.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>event_effectiveness_2</t>
+          <t>event_value_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Event Effectiveness</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>Event Value 2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Please select multiple options.</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>event_value_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Event Value</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>improvement_areas_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Improvement Areas</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>recommendations_3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Recommendations</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>comments_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>event_attendance_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Event Attendance</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>event_satisfaction_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Event Satisfaction</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1036,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1069,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>1-10</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1086,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>11-20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>11-20</t>
         </is>
       </c>
     </row>
@@ -1165,46 +1103,46 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>21-50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>21-50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>event_satisfaction_choices</t>
+          <t>event_attendance_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>51-100</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>51-100</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>event_satisfaction_choices</t>
+          <t>event_attendance_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>101_or_more</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>101 or more</t>
         </is>
       </c>
     </row>
@@ -1216,522 +1154,488 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>event_effectiveness_choices</t>
+          <t>event_satisfaction_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>event_effectiveness_choices</t>
+          <t>event_satisfaction_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>not_very_satisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Not Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>event_effectiveness_choices</t>
+          <t>event_satisfaction_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>not_satisfied_at_all</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Not Satisfied At All</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>event_value_choices</t>
+          <t>event_effectiveness_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>highly_effective</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Highly Effective</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>event_value_choices</t>
+          <t>event_effectiveness_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Somewhat Effective</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>event_value_choices</t>
+          <t>event_effectiveness_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>not_very_effective</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Not Very Effective</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>improvement_areas_2_choices</t>
+          <t>event_effectiveness_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>not_effective_at_all</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Not Effective At All</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>improvement_areas_2_choices</t>
+          <t>event_value_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>high_value</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>High Value</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>improvement_areas_2_choices</t>
+          <t>event_value_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>medium_value</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Medium Value</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>event_attendance_2_choices</t>
+          <t>event_value_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>low_value</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Low Value</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>event_attendance_2_choices</t>
+          <t>event_value_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No Value</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>event_attendance_2_choices</t>
+          <t>improvement_areas_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>event_content</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Event Content</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>event_satisfaction_2_choices</t>
+          <t>improvement_areas_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>event_organization</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Event Organization</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>event_satisfaction_2_choices</t>
+          <t>improvement_areas_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>event_promotion</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Event Promotion</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>event_satisfaction_2_choices</t>
+          <t>improvement_areas_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>event_follow-up</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Event Follow-up</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>event_effectiveness_2_choices</t>
+          <t>event_attendance_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>1-10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>1-10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>event_effectiveness_2_choices</t>
+          <t>event_attendance_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>11-20</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>11-20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>event_effectiveness_2_choices</t>
+          <t>event_attendance_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>21-50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>21-50</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>event_value_2_choices</t>
+          <t>event_attendance_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>51-100</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>51-100</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>event_value_2_choices</t>
+          <t>event_attendance_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>101_or_more</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>101 or more</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>event_value_2_choices</t>
+          <t>event_effectiveness_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>highly_effective</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Highly Effective</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>improvement_areas_3_choices</t>
+          <t>event_effectiveness_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>somewhat_effective</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Somewhat Effective</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>improvement_areas_3_choices</t>
+          <t>event_effectiveness_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>not_very_effective</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Not Very Effective</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>improvement_areas_3_choices</t>
+          <t>event_effectiveness_2_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>not_effective_at_all</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Not Effective At All</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>event_attendance_3_choices</t>
+          <t>event_value_2_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>high_value</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>High Value</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>event_attendance_3_choices</t>
+          <t>event_value_2_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>medium_value</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Medium Value</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>event_attendance_3_choices</t>
+          <t>event_value_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>low_value</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Low Value</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>event_satisfaction_3_choices</t>
+          <t>event_value_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no_value</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>event_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>event_satisfaction_3_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Option 3</t>
+          <t>No Value</t>
         </is>
       </c>
     </row>
